--- a/partner_results/imr/ClassMissingGermanLabel_imr.xlsx
+++ b/partner_results/imr/ClassMissingGermanLabel_imr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,22 +455,30 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>distance between sensor and extrudate [imr]</t>
+          <t>surface of extrudate [imr]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>relational quality</t>
+          <t>surface layer (fiat object part)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>uppermost layer of the extrudate</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -496,46 +504,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>extrudate norm [imr]</t>
+          <t>distance between sensor and extrudate [imr]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>relational quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>extrudate norm [imr]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>ideal dimensions and shape of the
 extrudate defined by the manufacturer</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>surface of extrudate [imr]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>surface layer (fiat object part)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>uppermost layer of the extrudate</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>measurement quality [imr]</t>
+          <t>shape [imr]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -546,10 +554,29 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>A morphological quality inhering in a bearer by virtue of the bearer's ratios of distances between its features (points, edges, surfaces and also holes etc).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>measurement quality [imr]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>In relation to optical measuring methods, a rating for the precision of a reconstructed measurement object.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
